--- a/Final Year Diseases Dataset.xlsx
+++ b/Final Year Diseases Dataset.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Diseases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1416,6 +1416,4198 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Typhoid Fever</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prolonged high fever, headache, weakness, fatigue, abdominal pain, constipation or diarrhea, loss of appetite, rose spots on chest, dry cough</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sudarshan Churna (₹80 Rs) - Reduces fever and infection; Kumari (Aloe vera) (₹45 Rs) - Cools the system; Amalaki (₹50 Rs) - Boosts immunity</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ceftriaxone (₹90 Rs) - Antibiotic for typhoid; Azithromycin (₹85 Rs) - Alternative antibiotic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Drink boiled water and fluids. Rest completely. Eat soft, easily digestible food. Complete the full antibiotic course. Wash hands regularly.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>General Physician / Infectious Disease Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>high fever, cough, runny nose, red watery eyes, white spots inside mouth, red rash spreading from face down the body, fatigue</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tulsi drops (₹50 Rs) - Antiviral and immune support; Trikatu churna (₹40 Rs) - Clears congestion; Neem bath (₹30 Rs) - Soothes skin rash</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Paracetamol (₹15 Rs) - Reduces fever; Vitamin A supplements (₹20 Rs) - Reduces complications</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Rest and isolate to prevent spread. Offer plenty of fluids. Use a cool-mist humidifier. Vaccination (MMR) is the best prevention.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>General Physician / Pediatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>swollen painful salivary glands, fever, headache, earache on chewing, fatigue, jaw pain, loss of appetite, muscle aches</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dashamoola Kwath (₹90 Rs) - Reduces gland swelling; Honey and ginger (₹40 Rs) - Soothes throat; Guduchi (₹60 Rs) - Antiviral support</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Paracetamol (₹15 Rs) - Pain and fever relief; Warm compresses along with analgesics</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Rest and isolate until swelling subsides. Apply warm or cold compresses to the swollen area. Drink fluids and eat soft foods. Avoid acidic foods.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>General Physician / Pediatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Rubella (German Measles)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>low-grade fever, pink rash starting on face and spreading down, mild headache, runny nose, swollen tender lymph nodes, joint pain, red eyes</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Neem capsules (₹60 Rs) - Blood purifier; Manjistha (₹80 Rs) - Skin detox; Giloy (₹60 Rs) - Immune booster</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Paracetamol (₹15 Rs) - For fever and aches; Rest and supportive care</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Rest and hydrate well. Avoid contact with pregnant women. Vaccination (MMR) prevents infection. Isolate for about a week after rash appears.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Whooping Cough (Pertussis)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>severe coughing fits, whooping sound on breathing in, cough ending in vomiting, runny nose, low fever, fatigue, breathlessness</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sitopaladi Churna (₹80 Rs) - Relieves cough; Vasaka syrup (₹65 Rs) - Calms bronchial spasm; Honey and black pepper (₹30 Rs) - Soothes throat</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Azithromycin (₹80 Rs) - Antibiotic for pertussis; Cough syrup to relieve symptoms</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Finish the prescribed antibiotics. Use a humidifier. Eat small frequent meals. Get vaccinated (DPT/Tdap) for you and children.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>General Physician / Pediatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>stiff jaw muscles, painful muscle spasms, stiffness in neck and abdomen, difficulty swallowing, fever, sweating, rapid heart rate</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Emergency care needed; post-exposure Ayurvedic tonic - Shatavari (₹90 Rs) - Nerve tonic; Ashwagandha (₹120 Rs) - Muscle recovery</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tetanus toxoid vaccine (₹150 Rs) - Protection; Tetanus immunoglobulin (₹400 Rs) - Immediate neutralization; Diazepam (₹30 Rs) - Muscle spasms</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Seek emergency medical care immediately. Complete the tetanus vaccination series. Clean wounds thoroughly with soap and water.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Emergency Medicine / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Scarlet Fever</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sore throat, red rash like sandpaper, high fever, flushed face with pale ring around mouth, strawberry tongue, red lines in skin folds</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tulsi tea (₹30 Rs) - Antipyretic; Haridra (Turmeric) (₹40 Rs) - Anti-inflammatory; Gargling with Triphala water (₹20 Rs) - Soothes throat</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Amoxicillin (₹50 Rs) - Antibiotic; Ibuprofen (₹25 Rs) - Reduces fever and pain</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Complete the full antibiotic course. Gargle with warm salt water. Stay hydrated. Rest and isolate to avoid spreading.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>General Physician / Pediatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>high fever, severe headache, muscle aches especially calves, chills, red eyes, abdominal pain, nausea, vomiting, jaundice</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Giloy juice (₹60 Rs) - Immune support; Kutki (₹100 Rs) - Liver protection; Tulsi (₹50 Rs) - Antipyretic</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Doxycycline (₹70 Rs) - Antibiotic; Paracetamol (₹15 Rs) - Fever relief</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Complete antibiotics as prescribed. Drink safe boiled water. Avoid contact with contaminated water. Control rodents near home.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>General Physician / Infectious Disease Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hand, Foot and Mouth Disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fever, sore throat, painful red blisters on hands, blisters on feet, mouth ulcers, poor appetite, irritability, drooling in children</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Triphala mouth rinse (₹50 Rs) - Heals mouth ulcers; Neem bath (₹30 Rs) - Soothes blisters; Honey (₹40 Rs) - Soothes ulcers</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Paracetamol (₹15 Rs) - Fever and pain; Oral rehydration for fluid balance, soothing mouth gel</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Give cool, soft foods and fluids. Avoid spicy and acidic foods. Keep blisters clean. Ensure good hand hygiene.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pediatrician / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Viral Gastroenteritis (Stomach Flu)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>watery diarrhea, stomach cramps, nausea, vomiting, low-grade fever, headache, muscle aches, dehydration, bloating</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Kutajarishta (₹80 Rs) - Controls diarrhea; Pomegranate juice (₹50 Rs) - Astringent; Ginger and honey tea (₹30 Rs) - Settles the stomach</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ORS sachets (₹20 Rs) - Prevents dehydration; Zinc tablets (₹15 Rs) - Shortens illness; Antiemetic if needed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Stay well hydrated with ORS and clear fluids. Eat bland foods (bananas, rice, toast). Wash hands frequently. Avoid dairy and fried food.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>General Physician / Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Food Poisoning</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>nausea, vomiting, watery diarrhea, stomach cramps, fever, weakness, dehydration, loss of appetite, headache</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ginger infusion (₹30 Rs) - Soothes the stomach; Pomegranate rind decoction (₹40 Rs) - Controls diarrhea; Ajwain water (₹25 Rs) - Digestion</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ORS sachets (₹20 Rs) - Rehydration; Anti-diarrheal only if prescribed; Antibiotics only for bacterial causes</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Rest your stomach with small sips of water. Rehydrate with ORS. Avoid solid food until vomiting stops. Seek care if blood in stool or high fever.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>General Physician / Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tuberculosis (TB)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>persistent cough with blood in sputum, unexplained weight loss, night sweats, low-grade evening fever, chest pain, fatigue, loss of appetite</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Vasa (₹60 Rs) - Lung tonic; Sitopaladi churna (₹80 Rs) - Respiratory support; Ashwagandha (₹120 Rs) - Restores strength</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Isoniazid + Rifampicin combination (₹120 Rs) - Anti-TB therapy (DOTS); Pyrazinamide and Ethambutol per regimen</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Complete the full 6-month DOTS treatment. Maintain good nutrition. Cover your mouth and use masks. Regular sputum and follow-up tests.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pulmonologist / TB Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>jaundice, dark urine, pale stools, fatigue, nausea, vomiting, abdominal pain, fever, loss of appetite</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kutki (₹100 Rs) - Liver protective; Bhumi Amla (₹70 Rs) - Liver regeneration; Sugarcane juice (₹20 Rs) - Liver tonic</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Supportive care; fluids and rest; test liver function; vaccination for prevention</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Rest completely and eat a light diet. Avoid alcohol and fatty foods. Wash hands and drink boiled water. Vaccination prevents infection.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Hepatologist / Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>jaundice, fatigue, dark urine, abdominal pain, nausea, loss of appetite, joint pain, fever, easy bruising</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Kutki (₹100 Rs) - Hepatoprotective; Guduchi (₹60 Rs) - Immune modulator; Punarnava (₹70 Rs) - Supports liver</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tenofovir (₹150 Rs) - Antiviral; Entecavir (₹200 Rs) - Alternative; Hepatitis B vaccine for prevention</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Complete antiviral therapy under specialist guidance. Avoid alcohol completely. Use protection during sex. Never share needles. Get vaccinated.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hepatologist / Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Shingles (Herpes Zoster)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>painful burning blistering rash on one side, tingling before rash, fever, headache, chills, fatigue, sensitivity to touch</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Neem paste (₹45 Rs) - Antiviral; Manjistha (₹80 Rs) - Blood purifier; Guduchi (₹60 Rs) - Immune support</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Acyclovir (₹120 Rs) - Antiviral; Gabapentin (₹70 Rs) - Nerve pain; Calamine lotion (₹50 Rs) - Itch relief</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Start antivirals within 72 hours of rash. Keep rash clean and dry. Use cool compresses. Get the shingles vaccine if over 50.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dermatologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ringworm (Tinea)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>circular itchy red patches, raised scaly border, clearing center, itching, peeling skin, broken blisters, spread to other areas</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Neem leaf paste (₹35 Rs) - Antifungal; Turmeric paste (₹40 Rs) - Anti-inflammatory; Garlic oil (₹40 Rs) - Antifungal</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Clotrimazole cream (₹40 Rs) - Antifungal; Terbinafine (₹90 Rs) - Oral antifungal</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Apply antifungal cream for at least 2-4 weeks. Keep the skin dry. Wash clothes and towels in hot water. Avoid sharing personal items.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Scabies</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>intense itching worse at night, thin burrow lines on skin, bumps and blisters, itching between fingers, rash on wrists and waist, sores from scratching</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Neem oil (₹50 Rs) - Kills mites; Turmeric and neem bath (₹30 Rs) - Soothes itching; Kutaja (₹70 Rs) - Antiparasitic</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Permethrin cream (₹60 Rs) - Kills scabies mites; Ivermectin (₹80 Rs) - Oral antiparasitic; antihistamine for itching</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Treat all household contacts at the same time. Wash bedding and clothes in hot water. Apply cream to the whole body. Vacuum furniture.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cellulitis</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>red swollen painful skin, warmth over the area, fever, chills, blisters, skin that looks dimpled, tenderness, red streaks</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Manjistha (₹80 Rs) - Blood purifier; Neem capsules (₹60 Rs) - Antibacterial; Turmeric milk (₹30 Rs) - Anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Cephalexin (₹60 Rs) - Antibiotic; Clindamycin (₹120 Rs) - If resistant; pain relievers</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Take antibiotics as prescribed and finish the course. Elevate the affected limb. Apply cool compresses. Watch for spreading redness.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dermatologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>sudden high fever, severe joint pain and stiffness, rash, headache, muscle pain, fatigue, swelling in joints, nausea</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Giloy juice (₹60 Rs) - Reduces fever and joint pain; Dashamoola kwath (₹90 Rs) - Joint and muscle pain; Ashwagandha (₹120 Rs) - Recovery</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Paracetamol (₹15 Rs) - Fever and pain (avoid aspirin); adequate hydration</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Rest and hydrate well. Use mosquito repellents and nets. Apply warm compresses to stiff joints. Consult a doctor for persisting joint pain.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>General Physician / Infectious Disease Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Rheumatic Fever</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fever, painful swollen joints, chest pain, heart murmur, tiredness, jerky uncontrollable movements, skin rash, nodules under skin</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Soothing cardiac tonics - Arjuna (₹80 Rs) - Heart support; Ashwagandha (₹120 Rs) - Anti-inflammatory; Guduchi (₹60 Rs) - Immunity</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Penicillin (₹40 Rs) - Treats streptococcal infection; Aspirin or other anti-inflammatory; steroids for severe cases</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Complete antibiotics to treat strep throat. Long-term penicillin prophylaxis needed. Bed rest during active phase. Regular heart check-ups.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Cardiologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sudden high fever, severe headache, stiff neck, nausea, vomiting, sensitivity to light, confusion, seizures, drowsiness</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Emergency care required; Ayurvedic supportive care after stabilization - Brahmi (₹90 Rs) - Nerve support</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ceftriaxone (₹90 Rs) - IV antibiotic; Dexamethasone (₹30 Rs) - Reduces inflammation; fluids and supportive care</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Seek emergency medical care immediately. Complete the full antibiotic course. Rest in a quiet dark room. Vaccination prevents many causes.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Emergency Medicine / Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Encephalitis</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fever, severe headache, confusion, seizures, stiff neck, sensitivity to light, drowsiness, irritability, muscle weakness</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Emergency care required; Brahmi (₹90 Rs) - Later nerve recovery; Ashwagandha (₹120 Rs) - Strength support</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Antiviral therapy (Acyclovir) (₹120 Rs); supportive care; anti-seizure medication; IV fluids</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Seek emergency care immediately. Hospital monitoring required. Ensure vaccination coverage in endemic areas. Mosquito control reduces risk.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Emergency Medicine / Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HIV/AIDS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>fever, swollen lymph nodes, sore throat, fatigue, night sweats, unexplained weight loss, recurrent infections, skin rashes, mouth sores</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Immune strength; Guduchi (₹60 Rs) - Immunity modulator; Tulsi (₹50 Rs) - Antimicrobial support</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Antiretroviral therapy (ART) (Integrated counselling); cotrimoxazole prophylaxis for opportunistic infections</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Start ART immediately and never miss doses. Regular CD4 and viral load tests. Safe practices prevent transmission. Eat a nutritious diet.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Infectious Disease Specialist / Antiretroviral Therapy Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Coronary Artery Disease (Angina)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>chest pain or pressure, pain radiating to arm and jaw, shortness of breath, fatigue, sweating, dizziness, palpitations</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Arjuna bark powder (₹80 Rs) - Strengthens heart muscle; Ashwagandha (₹120 Rs) - Reduces stress; Garlic capsules (₹60 Rs) - Improves circulation</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Aspirin (₹10 Rs) - Antiplatelet; Atorvastatin (₹80 Rs) - Lowers cholesterol; Nitroglycerin (₹50 Rs) - Relieves chest pain</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Adopt a heart-healthy diet low in salt and fat. Exercise under supervision. Quit smoking. Manage stress and blood pressure. Emergency care for severe pain.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Heart Failure</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>shortness of breath, swelling in legs and ankles, fatigue, rapid weight gain from fluid, persistent cough, wheezing, rapid heartbeat, abdominal swelling</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Arjuna (₹80 Rs) - Cardiac tonic; Punarnava (₹70 Rs) - Reduces fluid retention; Ashwagandha (₹120 Rs) - Supports heart function</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Furosemide (₹20 Rs) - Removes excess fluid; Enalapril (₹40 Rs) - Reduces heart load; Metoprolol (₹45 Rs) - Slows and strengthens heartbeat</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Follow a low-salt diet and monitor daily weight. Take medicines exactly as prescribed. Avoid alcohol and smoking. Regular cardiology follow-up.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Atrial Fibrillation</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>irregular heartbeats, palpitations, racing heart, fatigue, shortness of breath, dizziness, chest discomfort, lightheadedness</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Arjuna (₹80 Rs) - Regulates heartbeat; Brahmi (₹90 Rs) - Calms the nervous system; Deep breathing with meditation</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Beta-blockers (Metoprolol ₹45 Rs) - Controls rate; blood thinners (Rivaroxaban ₹200 Rs) - Prevents stroke; cardioversion if needed</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Limit alcohol and caffeine. Manage stress and sleep well. Take blood thinners exactly as directed. Regular ECG monitoring.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Cholesterol (Hyperlipidemia)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>often no symptoms, fatty deposits under skin (xanthomas), chest pain, fatigue, shortness of breath, yellowish patches near eyes</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Garlic capsules (₹60 Rs) - Lowers LDL; Guggulu (₹90 Rs) - Reduces cholesterol; Triphala (₹50 Rs) - Cleans the system</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Atorvastatin (₹80 Rs) - LDL lowering; Rosuvastatin (₹100 Rs) - Potent statin; lifestyle changes essential</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Reduce saturated fats and trans fats. Exercise 30-45 minutes daily. Eat fiber-rich foods and omega-3. Get lipid profile checked yearly.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Cardiologist / Internal Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Deep Vein Thrombosis</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>swelling in one leg, pain and tenderness, warm skin, red discoloration, leg ache that worsens, visibly engorged veins</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Supportive anticoagulant herbs under guidance - Ginger (₹40 Rs) - Improves circulation; Garlic (₹60 Rs) - Blood thinner support</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Heparin injection (₹300 Rs) - Immediate anticoagulant; Warfarin (₹40 Rs) - Long-term thinning; compression stockings</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Seek urgent care if sudden chest pain or breathlessness. Take blood thinners as prescribed. Move regularly and avoid prolonged sitting. Use compression stockings.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vascular Surgeon / Cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Varicose Veins</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>bulging twisted veins in legs, heavy aching legs, swelling in ankles, itchy skin over veins, leg cramps at night, skin discoloration</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Manjistha (₹80 Rs) - Improves circulation; Ashwagandha (₹120 Rs) - Reduces inflammation; Hirudotherapy oils for massage</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Compression stockings; Diosmin (₹90 Rs) - Improves vein tone; sclerotherapy or surgery for severe cases</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Elevate legs regularly. Avoid prolonged standing. Exercise to improve circulation. Wear compression stockings. Surgery for severe pain.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vascular Surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Peripheral Artery Disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>leg pain on walking that improves with rest, numbness or weakness in legs, cold lower leg, sores on feet that won't heal, pale skin, weak pulses</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Garlic (₹60 Rs) - Improves blood flow; Ashwagandha (₹120 Rs) - Circulation tonic; Guggulu (₹90 Rs) - Reduces artery inflammation</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Aspirin (₹10 Rs) - Antiplatelet; Atorvastatin (₹80 Rs) - Vascular protection; supervised walking programs</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Quit smoking completely. Walk daily as tolerated. Manage diabetes and blood pressure. Inspect feet daily for sores. See a vascular specialist.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vascular Surgeon / Cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Myocarditis</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>chest pain, fever, fatigue, shortness of breath, rapid or irregular heartbeat, fluid retention with leg swelling, flu-like symptoms</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Strict rest; Arjuna (₹80 Rs) - Cardiac support after stabilization; Guduchi (₹60 Rs) - Reduces inflammation</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ACE inhibitors; beta-blockers; anti-inflammatory steroids; antiviral or antibiotics for cause</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Strict bed rest until recovery. Avoid strenuous exercise for months. Follow cardiologist follow-up. Report any chest pain or palpitations at once.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Pericarditis</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>sharp chest pain worsening on breathing or lying down, relieved by sitting forward, fever, fatigue, cough, shortness of breath, palpitations</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Arjuna (₹80 Rs) - Heart support; Turmeric (₹40 Rs) - Anti-inflammatory; Rest and warm compress on chest</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ibuprofen (₹25 Rs) - Reduces inflammation; Colchicine (₹80 Rs) - Prevents recurrence; steroids for resistant cases</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Rest and avoid heavy exertion. Take anti-inflammatories as directed. Avoid alcohol. Urgent care if pain is severe or breathing difficult.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>COPD (Chronic Obstructive Pulmonary Disease)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>chronic cough with mucus, shortness of breath that worsens, wheezing, chest tightness, frequent respiratory infections, low energy, weight loss</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Vasaka (₹60 Rs) - Expectorant; Kantakari (₹55 Rs) - Clears airways; Licorice (Mulethi) (₹45 Rs) - Soothes airways</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Salbutamol inhaler (₹120 Rs) - Bronchodilator; Tiotropium (₹180 Rs) - Long-acting bronchodilator; inhaled corticosteroids</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Quit smoking and avoid secondhand smoke. Use inhalers daily as prescribed. Do breathing exercises and pulmonary rehab. Get flu and pneumonia vaccines.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Pulmonologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Laryngitis</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>hoarse voice, weak or lost voice, sore throat, dry cough, feeling of tickling in throat, fever, fatigue, dry scratchy throat</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Mulethi (Licorice) (₹45 Rs) - Soothes voice box; Honey and ginger tea (₹30 Rs) - Relieves irritation; Warm saline gargles (₹10 Rs)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Voice rest; steam inhalation; lozenges; treat underlying infection if bacterial</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Rest your voice completely. Drink warm fluids. Avoid whispering and irritants. Humidify the air. See ENT if hoarseness lasts over 2 weeks.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ENT Specialist (Otorhinolaryngologist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Tonsillitis</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>sore throat, white patches on tonsils, difficulty swallowing, fever, swollen tonsils, bad breath, ear pain, swollen neck glands</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Khadira (Akashia) gargles (₹40 Rs) - Antiseptic; Honey and turmeric (₹40 Rs) - Soothes inflammation; Tulsi tea (₹30 Rs) - Antipyretic</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Amoxicillin (₹50 Rs) - Antibiotic; Ibuprofen (₹25 Rs) - Pain and fever; warm salt water gargles</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Gargle with warm salt water. Drink warm fluids. Complete antibiotics. Rest. Surgery for recurrent tonsillitis when needed.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ENT Specialist (Otorhinolaryngologist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Pharyngitis (Sore Throat)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sore raw throat, pain on swallowing, scratchy feeling, tonsil redness, fever, swollen glands, hoarseness, cold symptoms</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Honey and ginger (₹40 Rs) - Soothes throat; Licorice tea (₹45 Rs) - Anti-inflammatory; Tulsi gargles (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Paracetamol (₹15 Rs) - Pain relief; lozenges; antibiotics only if bacterial (Amoxicillin ₹50 Rs)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Gargle with warm salt water. Drink warm fluids with honey. Rest your voice. Avoid smoking and dry air. See doctor if strep suspected.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>General Physician / ENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Croup</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>barking cough especially at night, hoarse voice, fever, noisy breathing on inhale, runny nose, chest retractions in children</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Steam inhalation with Tulsi and eucalyptus (₹30 Rs) - Opens airways; warm onion-honey syrup (₹40 Rs) - Calms cough</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Dexamethasone (₹30 Rs) - Reduces airway swelling; racemic epinephrine for severe cases; humidified air</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Keep the child calm and upright. Use a humidifier or steam. Offer warm fluids. Seek emergency care if breathing difficulty worsens.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Pediatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Pleurisy</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>sharp chest pain worse on breathing or coughing, shortness of breath, fever, cough, pain radiating to shoulder, rapid breathing</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vasaka syrup (₹65 Rs) - Lung support; Turmeric paste compress (₹40 Rs) - External pain relief; Guduchi (₹60 Rs) - Anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ibuprofen (₹25 Rs) - Pain and inflammation; treat underlying cause (antibiotics for infection, anticoagulants for clot)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Rest and avoid exertion. Take pain relief as directed. Treat the underlying cause. Urgent care for severe breathlessness.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Pulmonologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pulmonary Embolism</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>sudden shortness of breath, sharp chest pain, cough with blood, rapid heartbeat, sweating, dizziness, fainting, anxiety</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>This is an emergency; after stabilization supportive herbs including Arjuna (₹80 Rs) - Heart support</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Emergency: heparin (₹300 Rs) - Anticoagulant; thrombolytics for massive PE; long-term DOACs</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Call emergency services immediately. Take blood thinners as prescribed. Move legs during long travel. Stop smoking.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Emergency Medicine / Pulmonologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sleep Apnea</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>loud snoring, gasping or choking during sleep, daytime sleepiness, morning headaches, dry mouth on waking, irritability, poor concentration</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Reduces stress; Shankhpushpi (₹70 Rs) - Calming; Nasal oil (Nasya) (₹60 Rs) - Opens airways</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CPAP machine therapy; oral appliances; weight-loss programs; surgery for obstructive causes</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Lose weight and avoid alcohol before bed. Sleep on your side. Use CPAP as prescribed. Avoid sedatives. Consult a sleep specialist.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sleep Medicine Specialist / Pulmonologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fever, dry cough, fatigue, loss of taste or smell, sore throat, headache, body aches, shortness of breath, chest tightness</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Giloy (₹60 Rs) - Immunity; Tulsi and honey kadha (₹30 Rs) - Soothing; Ashwagandha (₹120 Rs) - Recovery</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Antipyretics (Paracetamol ₹15 Rs); oxygen support in severe cases; antiviral therapy for high-risk patients</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Isolate and monitor oxygen levels. Rest and hydrate. Get vaccinated and boosted. Emergency care for breathing difficulty.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>General Physician / Infectious Disease Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gastroesophageal Reflux Disease (GERD)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>heartburn, acid regurgitation, chest pain, difficulty swallowing, chronic cough, hoarseness, sour taste in mouth, burping</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Avipattikar churna (₹70 Rs) - Balances acidity; Yashtimadhu (₹80 Rs) - Soothes stomach; Amla (₹40 Rs) - Natural antacid</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Omeprazole (₹30 Rs) - Suppresses acid; Antacids (₹50 Rs) - Quick relief; Domperidone (₹40 Rs) - Improves emptying</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Eat small frequent meals. Avoid lying down 3 hours after meals. Elevate your bed head. Avoid spicy, oily and acidic foods. Lose weight if overweight.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Appendicitis</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>pain starting near navel then moving to lower right abdomen, sharp pain worsens with movement, nausea, vomiting, loss of appetite, fever, constipation or diarrhea</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>This is a surgical emergency; warm the pain area only after surgeon's advice - post-op herbs like Kutki (₹100 Rs) - Healing</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Emergency appendectomy (surgery); IV antibiotics in hospital</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Seek emergency care immediately. Do not eat or drink and do not use laxatives. Surgery is the definitive treatment.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Emergency Medicine / Surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Gallstones</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>sudden severe pain in upper right abdomen, pain after fatty meals, nausea, vomiting, pain radiating to right shoulder, bloating, jaundice if bile duct blocked</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Punarnava (₹70 Rs) - Anti-inflammatory; Varuna (₹85 Rs) - Dissolves stones; Trikatu (₹40 Rs) - Aids fat digestion</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pain relievers (Diclofenac ₹25 Rs); ursodeoxycholic acid (₹80 Rs) - Dissolves small stones; surgery (cholecystectomy) if recurrent</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Limit fatty and fried foods. Maintain a healthy weight. Eat high-fiber foods. Seek urgent care for jaundice or severe pain. Surgery for recurring attacks.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gastroenterologist / Surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cirrhosis of the Liver</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>fatigue, weakness, easy bruising, swelling in legs and abdomen, jaundice, itchy skin, confusion, weight loss, dark urine, spider angiomas</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Kutki (₹100 Rs) - Liver protective; Bhumi Amla (₹70 Rs) - Regenerative; Punarnava (₹70 Rs) - Reduces fluid</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Diuretics (Spironolactone ₹45 Rs) - Fluid removal; beta-blockers - prevent bleeding; lactulose for confusion; liver transplant in advanced cases</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Stop alcohol completely. Low-salt diet. Monitor for swelling and confusion. Regular specialist follow-up. Vaccinate against hepatitis A and B.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Hepatologist / Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Celiac Disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>diarrhea, bloating, gas, weight loss, fatigue, anemia, itchy skin rash, abdominal pain, bone or joint pain, mouth ulcers</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Shatavari (₹90 Rs) - Heals intestinal lining; Yashtimadhu (₹80 Rs) - Soothes gut; Triphala (₹50 Rs) - Digestive balance</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Strict gluten-free diet; vitamin and mineral supplements (B12, iron, calcium); no specific drug therapy</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Follow a strict lifelong gluten-free diet. Read food labels for hidden gluten. Supplements for deficiencies. Regular follow-up and bone-density tests.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gastroenterologist / Nutritionist</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Crohn's Disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>chronic diarrhea, abdominal pain, weight loss, fatigue, fever, mouth sores, reduced appetite, blood in stool, joint pain</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Kutajarishta (₹80 Rs) - Calms gut; Slippery elm-like soothing herbs (Aloe) (₹45 Rs) - Coats intestine; Ashwagandha (₹120 Rs) - Restoration</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mesalamine (₹95 Rs) - Reduces gut inflammation; steroids (Budesonide ₹150 Rs); biologics (Infliximab) for severe disease</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Follow a nutritionist-guided diet and food diary. Avoid NSAIDs and smoking. Manage stress. Take immunomodulators exactly as prescribed.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ulcerative Colitis</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>bloody diarrhea, abdominal cramps, rectal pain, urgency to defecate, weight loss, fatigue, fever, reduced appetite</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Kutajarishta (₹80 Rs) - Controls diarrhea; Dhanyaka (Coriander) (₹20 Rs) - Soothes gut; Shatavari (₹90 Rs) - Healing</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mesalamine (₹95 Rs) - First-line; steroids for flares; immunomodulators (Azathioprine ₹100 Rs)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Follow the prescribed medication plan. Keep a food diary and avoid triggers. Stay hydrated. Regular colonoscopies for monitoring.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Constipation</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>fewer than three bowel movements a week, hard dry stools, straining, bloating, abdominal discomfort, feeling of incomplete evacuation, small stools</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Triphala (₹50 Rs) - Gentle laxative; Castor oil (warm) (₹30 Rs) - Lubricant; Isabgol (Psyllium) (₹30 Rs) - Bulk-forming fiber</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Lactulose (₹45 Rs) - Osmotic laxative; Bisacodyl (₹20 Rs) - Stimulant laxative; stool softeners</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Drink 2-3 liters of water daily. Eat fiber-rich fruits and vegetables. Exercise regularly. Set a regular toilet routine. Avoid delaying the urge.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gastroenterologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Hemorrhoids (Piles)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>bleeding during bowel movements, painful lump near anus, itching and irritation, swelling around anus, pain and discomfort, painless bright red blood</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Dhak (Palash) flowers (₹50 Rs) - Stops bleeding; Avipattikar churna (₹70 Rs) - Regulates digestion; Warm sitz bath with Triphala (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Hydrocortisone cream (₹35 Rs) - Reduces swelling; stool softeners; rubber band ligation; surgery for large piles</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Eat high-fiber foods and drink water. Avoid straining on the toilet. Warm sitz baths daily. Don't sit too long. Severe bleeding needs a doctor.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gastroenterologist / Surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Pancreatitis</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>severe upper abdominal pain radiating to the back, nausea, vomiting, fever, rapid pulse, swollen tender abdomen, oily stools</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Emergency care; later supportive herbs - Ginger (₹40 Rs) - Anti-inflammatory; Shatavari (₹90 Rs) - Restores digestion</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>IV fluids and pain control in hospital; Pancreatic enzyme supplements (₹150 Rs); treat the underlying cause</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Seek urgent hospital care for severe pain. Stop alcohol completely. Follow a low-fat diet. Quit smoking. Manage gallstones and triglycerides.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Food Allergy</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>hives, swelling of lips and tongue, itching, abdominal pain, diarrhea, nausea, wheezing, dizziness, anaphylaxis in severe cases</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Emergency antihistamine herbs are not sufficient; after care - Amalaki (₹50 Rs) - Immune balance; Yashtimadhu (₹80 Rs) - Soothes</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Epinephrine auto-injector (₹450 Rs) - For anaphylaxis; antihistamines (Cetirizine ₹20 Rs); avoidance is key</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Identify and strictly avoid the offending food. Read labels carefully. Carry an epinephrine auto-injector if advised. Tell restaurants about allergies.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Allergist / Immunologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Non-Alcoholic Fatty Liver Disease (NAFLD)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>fatigue, mild right upper abdomen discomfort, unexplained weight gain, high triglycerides, enlarged liver, no symptoms in early stage</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Kutki (₹100 Rs) - Liver detox; Bhumi Amla (₹70 Rs) - Liver health; Triphala (₹50 Rs) - Metabolic balance</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Vitamin E in select cases; diabetes and cholesterol medications; weight management is the mainstay</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Lose 5-10% of body weight gradually. Cut sugar and refined carbs. Exercise 150 minutes weekly. Avoid alcohol. Repeat liver tests regularly.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Hepatologist / Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Diverticulitis</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>left lower abdominal pain, fever, nausea, vomiting, change in bowel habits, bloating, tenderness, constipation or diarrhea</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Liquid diet and rest initially; after acute phase - Kutajarishta (₹80 Rs) - Gut healing; Yashtimadhu (₹80 Rs) - Anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Antibiotics (Ciprofloxacin + Metronidazole ₹90 Rs); clear liquid diet; surgery for complications</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Temporarily follow a clear-liquid diet. Take full antibiotics course. Later add fiber slowly. See a doctor for fever or severe pain.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Dysentery (Amoebic)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>blood and mucus in stool, frequent loose stools, abdominal cramps, tenesmus, fever, weakness, nausea, dehydration</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Kutajarishta (₹80 Rs) - Controls dysentery; Pomegranate rind tea (₹40 Rs) - Astringent; Bilva (Bael) (₹50 Rs) - Gut tonic</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Metronidazole (₹35 Rs) - Antibiotic for amoeba; ORS for dehydration; rehydration salts</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Drink boiled water and ORS. Complete antibiotic course. Wash hands after toilet. Avoid raw foods in unhygienic settings.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>General Physician / Gastroenterologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Lactose Intolerance</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>bloating, gas, diarrhea after dairy, stomach cramps, nausea, rumbling sounds, loose stools, symptoms after milk products</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ginger infusion (₹30 Rs) - Improves digestion; Trikatu (₹40 Rs) - Digestive fire; Amalaki (₹50 Rs) - Balances</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Lactase enzyme tablets (₹80 Rs); calcium and vitamin D supplements; dietary lactose avoidance</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Reduce or avoid dairy, or choose lactose-free products. Take lactase tablets before dairy. Ensure adequate calcium from other sources.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gastroenterologist / Nutritionist</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Tension Headache</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>dull pressure or tight band pain around head, both-sided headache, neck and shoulder tightness, pain worsening late day, sensitivity to noise</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Brahmi (₹90 Rs) - Calms the mind; Shankhpushpi (₹70 Rs) - Relaxation; Massage oil on scalp and neck (₹60 Rs)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Ibuprofen (₹25 Rs) - Pain relief; muscle relaxants if needed; stress management</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Practice relaxation techniques and deep breathing. Maintain good posture. Use warm compresses on neck. Ensure regular sleep and meals.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Neurologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cluster Headache</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>severe one-sided head pain around the eye, red watery eye, nasal congestion on one side, restlessness, attacks in clusters, for hours for weeks</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Acute-phase supportive care; preventive - Brahmi (₹90 Rs) - Nerve support; Dashamoola massage (₹100 Rs)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Oxygen inhalation; Sumatriptan injection (₹150 Rs); Verapamil (₹60 Rs) - Preventive</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Avoid alcohol and smoking during cluster periods. Use oxygen as instructed. Follow preventive medication as prescribed. Keep an attack diary.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Epilepsy</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>recurrent seizures, convulsions, jerking of limbs, staring spells, confusion after seizure, sudden falls, loss of consciousness, aura before seizure</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Brahmi (₹90 Rs) - Nerve stabilizer; Ashwagandha (₹120 Rs) - Stress reduction; Shankhpushpi (₹70 Rs) - Sedative</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sodium valproate (₹55 Rs) - Anti-seizure; Levetiracetam (₹140 Rs) - Modern anticonvulsant; carbamazepine</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Take anti-seizure medicines regularly, never skip. Avoid alcohol and sleep deprivation. If a seizure lasts 5 minutes, call emergency services. Wear medical alert ID.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Parkinson's Disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>tremor in hands at rest, slow movements, stiff muscles, impaired posture and balance, loss of facial expression, soft or slurred speech, reduced arm swing</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Kapikachhu (Mucuna) (₹90 Rs) - Natural levodopa; Ashwagandha (₹120 Rs) - Supports nerves; Brahmi (₹90 Rs) - Cognitive support</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Levodopa-Carbidopa (₹120 Rs) - Dopamine replacement; dopamine agonists (Pramipexole ₹110 Rs)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Exercise daily with physiotherapy. Follow medication timing strictly. Adjust diet to avoid protein-medication interaction. Join support groups.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Stroke (Cerebrovascular Accident)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>sudden one-sided weakness or numbness, facial drooping, slurred speech, sudden confusion, severe headache, vision loss in one eye, difficulty walking, dizziness</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>This is an emergency; after recovery - Arjuna (₹80 Rs) - Circulation; Brahmi (₹90 Rs) - Brain recovery; Ashwagandha (₹120 Rs)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Emergency: clot-busting r-tPA within hours; blood thinners (Aspirin ₹10 Rs); statins; blood pressure control</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Call emergency services immediately at first signs (FAST: Face, Arm, Speech, Time). Rehabilitation is crucial. Control BP, diabetes, and cholesterol. Quit smoking.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Emergency Medicine / Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Alzheimer's Disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>memory loss disrupting daily life, confusion with time and place, difficulty with problem solving, misplacing things, withdrawal, mood changes, poor judgment</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Brahmi (₹90 Rs) - Memory support; Ashwagandha (₹120 Rs) - Mental calm; Shankhpushpi (₹70 Rs) - Cognitive tonic</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Donepezil (₹100 Rs) - Cholinesterase inhibitor; Memantine (₹130 Rs) - For moderate disease</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Maintain routine and familiar surroundings. Keep mentally and physically active. Manage other health conditions. Caregiver support is essential.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Neurologist / Geriatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>numbness or weakness in limbs, tingling, blurred vision, double vision, lack of coordination, fatigue, dizziness, bladder problems, spasticity</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Immune balance; Guduchi (₹60 Rs) - Modulates immunity; Brahmi (₹90 Rs) - Nerve support</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Corticosteroids for flares (Methylprednisolone); disease-modifying therapy (Interferon β, ₹450 Rs); physiotherapy</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Follow your disease-modifying therapy. Physiotherapy for mobility. Manage stress and avoid overheating. Regular neurology follow-up.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Bell's Palsy</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>sudden one-sided facial weakness, drooping eyelid and mouth, difficulty smiling or closing eye, drooling, ear pain, altered taste, dry eye</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bala oil massage (₹120 Rs) - Nerve strengthening; Mahanarayan oil (₹130 Rs) - Facial massage; Bacopa (₹90 Rs) - Nerve recovery</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Prednisolone (₹50 Rs) - Within 72 hours improves recovery; artificial tears for the eye</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Start steroids early. Protect the weak eye with eye drops and taping at night. Do gentle facial exercises. Most recover within months.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Vertigo (BPPV)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>spinning sensation triggered by head movement, loss of balance, nausea, vomiting, unsteady gait, dizziness lasting seconds to a minute</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Balance support; Brahmi (₹90 Rs) - Calms inner ear nerves; Nimba head oil massage (₹60 Rs)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Epley manoeuvre by a specialist; Betahistine (₹45 Rs) - Improves inner ear circulation; antihistamines for symptoms</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Perform the Epley manoeuvre with guidance. Avoid sudden head movements. Sit up slowly. Sleep with head slightly elevated. See ENT for persistent vertigo.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ENT / Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Peripheral Neuropathy</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>numbness and tingling in hands or feet, sharp burning pain, sensitivity to touch, muscle weakness, loss of balance, worsened at night</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bala (₹70 Rs) - Nerve tonic; Ashwagandha (₹120 Rs) - Nerve repair; Massage with Mahanarayan oil (₹130 Rs)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pregabalin (₹70 Rs) - Nerve pain; Amitriptyline (₹50 Rs) - Low-dose pain relief; vitamin B12 supplements</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Manage the underlying cause (diabetes control). Take pain medicines as prescribed. Check feet daily for injuries. Limit alcohol.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Anxiety Disorder</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>excessive worry, restlessness, irritability, difficulty concentrating, racing heart, muscle tension, sleep problems, sweating, feeling overwhelmed, avoiding situations</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Stress adaptogen; Brahmi (₹90 Rs) - Calms mind; Shankhpushpi (₹70 Rs) - Relaxing</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SSRIs (Escitalopram ₹70 Rs) - Long-term relief; short-term benzodiazepines; cognitive behavioral therapy</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Practice deep breathing and mindfulness. Regular exercise. Limit caffeine and alcohol. Consistent sleep schedule. Consider therapy.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Psychiatrist / Clinical Psychologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Depression</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>persistent sadness, loss of interest in activities, fatigue, sleep disturbance, appetite changes, feelings of worthlessness, poor concentration, thoughts of self-harm</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Mood support; Brahmi (₹90 Rs) - Mental clarity; Jatamansi (₹90 Rs) - Calming</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SSRIs (Sertraline ₹60 Rs); psychotherapy (CBT); exercise therapy</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Seek professional help. Take antidepressants as prescribed. Maintain routine and support network. If you have thoughts of self-harm, contact emergency services now.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Psychiatrist / Clinical Psychologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Bipolar Disorder</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>manic episodes with elevated mood, high energy, reduced need for sleep, grandiosity, rapid speech; depressive episodes with low mood, hopelessness, fatigue</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Supportive - Brahmi (₹90 Rs) - Mood balance; Ashwagandha (₹120 Rs) - Stability; regulated daily routine with meditation</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lithium (₹80 Rs) - Mood stabilizer; Lamotrigine (₹110 Rs); antipsychotics for mania</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Take mood stabilizers consistently, never stop abruptly. Regular blood tests for lithium levels. Maintain a stable sleep pattern. Involve family in care.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Psychiatrist</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Schizophrenia</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>hallucinations (hearing voices), delusions, disorganized speech, social withdrawal, reduced motivation, poor self-care, difficulty expressing emotion</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Supportive Ayurvedic care only - Brahmi (₹90 Rs) - Calming; Ashwagandha (₹120 Rs) - Reducing stress; family support and routine</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Antipsychotics (Risperidone ₹70 Rs, Olanzapine ₹60 Rs); long-acting injectables; psychosocial rehabilitation</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Stick to antipsychotic medication without interruption. Attend follow-ups. Build a supportive environment. Avoid alcohol and recreational drugs.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Psychiatrist</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ADHD (Attention Deficit Hyperactivity Disorder)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>inattention easily distracted, difficulty organising tasks, forgetfulness, fidgeting, excessive talking, interrupting, poor time management, impulsivity</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Brahmi (₹90 Rs) - Improves focus; Shankhpushpi (₹70 Rs) - Calms restlessness; structured daily routine</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Stimulants (Methylphenidate ₹80 Rs); non-stimulant (Atomoxetine ₹120 Rs); behavioral therapy</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Follow treatment and therapy plan. Use routines and reminders. Minimize distractions while studying. Regular exercise improves symptoms.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Psychiatrist / Pediatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Obsessive Compulsive Disorder (OCD)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>unwanted repeated thoughts (obsessions), repetitive rituals (compulsions), checking and washing behaviors, distress when rituals are disrupted, hoarding</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Brahmi (₹90 Rs) - Reduces mental rigidity; Ashwagandha (₹120 Rs) - Lowers anxiety; Jatamansi (₹90 Rs) - Calming</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SSRIs (Fluoxetine ₹55 Rs) - High dose; cognitive behavioral therapy with ERP; antipsychotic augmentation</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Commit to Cognitive Behavioral Therapy (ERP). Take SSRIs as prescribed. Avoid rituals gradually with therapist guidance. Family support helps.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Psychiatrist / Clinical Psychologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Panic Disorder</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>sudden intense fear attacks, racing heart, sweating, trembling, shortness of breath, chest tightness, dizziness, fear of losing control, avoidance of situations</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Calms nervous system; Brahmi (₹90 Rs) - Panic support; Slow breathing with peppermint oil (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SSRIs (Sertraline ₹60 Rs); CBT; short-term benzodiazepines only during recovery</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Learn breathing and grounding techniques. Exercise regularly. Limit caffeine. Attend therapy. Take medication as directed.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Psychiatrist / Clinical Psychologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Post-Traumatic Stress Disorder (PTSD)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>flashbacks, nightmares, intrusive memories, avoiding reminders, hypervigilance, irritability, difficulty sleeping, emotional numbness</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Stress adaptogen; Brahmi (₹90 Rs) - Mental calm; Jatamansi (₹90 Rs) - Sleep support</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SSRIs (Sertraline ₹60 Rs, Paroxetine ₹75 Rs); trauma-focused therapy (CBT/EMDR)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Engage in trauma-focused therapy. Take medication as prescribed. Build a support system. Practice grounding techniques and regular sleep.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Psychiatrist / Clinical Psychologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Restless Legs Syndrome</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>uncontrollable urge to move legs especially at night, creeping or crawling sensations, symptoms worse at rest, relief with movement, sleep disturbance</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Calming; Bala oil massage (₹120 Rs) - Leg relaxation; warm foot baths with Epsom salts (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Dopamine agonists (Ropinirole ₹90 Rs); gabapentin for sleep; iron supplements if deficient</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Check iron levels and supplement if low. Avoid caffeine and alcohol. Leg stretches and warm baths at bedtime. Maintain a sleep routine.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Neurologist / Sleep Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Hyperthyroidism</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>rapid heartbeat, weight loss despite normal appetite, sweating, tremors, anxiety, heat intolerance, frequent bowel movements, fatigue, bulging eyes</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Shanka pushpi (₹70 Rs) - Calms nerves; Ashwagandha (₹120 Rs) - Balances thyroid; Punarnava (₹70 Rs) - Anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Methimazole (₹60 Rs) - Reduces thyroid hormone; beta-blockers for symptoms; radioiodine or surgery for some</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Take antithyroid medicine regularly. Get TSH levels checked periodically. Avoid excess iodine. Manage stress and get enough rest.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Endocrinologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Hashimoto's Thyroiditis</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>fatigue, weight gain, cold intolerance, dry skin, hair thinning, constipation, muscle aches, depression, goiter, heavy menstruation</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Balances thyroid; Kanchanar guggulu (₹100 Rs) - Supports thyroid; Triphala (₹50 Rs) - Metabolism</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Levothyroxine (₹30 Rs) - Hormone replacement; regular TSH monitoring</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Take levothyroxine on an empty stomach each morning. Avoid soy near medication time. Regular TSH tests. Manage stress and sleep.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Endocrinologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Goiter (Enlarged Thyroid)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>swelling at the base of the neck, tightness in throat, cough, hoarseness, difficulty swallowing, breathing difficulty with large goiter</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Kanchanar guggulu (₹100 Rs) - Reduces gland swelling; Ashwagandha (₹120 Rs) - Thyroid balance; Varuna (₹85 Rs) - Supports neck glands</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Levothyroxine (₹30 Rs) if hypothyroid; iodine as appropriate; surgery for obstructive goiter</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Get thyroid function and ultrasound checked. Take medicines as prescribed. Ensure adequate (not excess) iodine. Surgery if swallowing becomes hard.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Endocrinologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Polycystic Ovary Syndrome (PCOS)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>irregular or missed periods, excess facial hair, acne, weight gain, hair thinning on scalp, difficulty conceiving, dark skin patches, mood changes</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Shatavari (₹90 Rs) - Hormonal balance; Ashwagandha (₹120 Rs) - Reduces insulin resistance; Kanchanar guggulu (₹100 Rs) - Cysts</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Metformin (₹35 Rs) - Improves insulin sensitivity; hormonal birth control for cycle regulation; fertility treatments if trying to conceive</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Lose 5-10% body weight with diet and exercise. Follow low-glycemic meals. Manage stress. Regular gynaecologist follow-up.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Gynaecologist / Endocrinologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Type 1 Diabetes</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>excessive thirst, frequent urination, extreme hunger, unexplained weight loss, fatigue, blurry vision, dry mouth, fruity-smelling breath</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Karela juice (₹50 Rs) - Supports sugar control; Jamun seed powder (₹60 Rs) - Helps glucose; Fenugreek (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Insulin injections (₹250 Rs) - Essential; regular blood glucose monitoring</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Insulin is essential - never miss doses. Monitor blood sugar frequently. Count carbohydrates and balance with insulin. Have a sick-day plan.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Endocrinologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Hypoglycemia</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>shakiness, sweating, rapid heartbeat, confusion, dizziness, hunger, irritability, blurred vision, seizure or unconsciousness in severe cases</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Post-event restoration - Guduchi (₹60 Rs); Ashwagandha (₹120 Rs) - Blood sugar balance</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Immediate: fast-acting glucose (glucose tablets / juice); glucagon injection for emergencies</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Treat immediately with 15g fast carbs and re-check in 15 minutes. Eat regular balanced meals. Let family know how to give glucagon.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Endocrinologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>no symptoms until fracture, back pain from vertebral crush, loss of height over time, stooped posture, easy fractures of wrist hip spine</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Bone strength; Godanti bhasma (₹90 Rs) - Calcium source; Tila (sesame) seeds (₹40 Rs) - Bone nutrition</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Calcium and vitamin D supplements; bisphosphonates (Alendronate ₹100 Rs); HRT in select cases</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Ensure calcium (1000-1200 mg) and vitamin D daily. Weight-bearing exercises. Avoid smoking and excess alcohol. Get a DEXA scan for at-risk people.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Endocrinologist / Orthopedic Surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Gout</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>sudden severe joint pain usually in big toe, swelling, redness, warmth, tenderness, recurrent attacks, difficulty walking</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Guduchi (₹60 Rs) - Reduces uric acid inflammation; Punarnava (₹70 Rs) - Purifies blood; Ginger compress (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Colchicine (₹30 Rs) - Acute attack relief; Allopurinol (₹50 Rs) - Prevents attacks; NSAIDs (Naproxen ₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Drink plenty of water. Limit purine-rich foods (red meat, organ meats, seafood) and alcohol. Manage weight. Take urate-lowering medicines regularly.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Rheumatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Addison's Disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>fatigue, weakness, weight loss, low blood pressure with dizziness, darkening of skin, salt craving, abdominal pain, nausea, depression</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Supportive - Ashwagandha (₹120 Rs) - Adrenal support; Shatavari (₹90 Rs) - Energy; Punarnava (₹70 Rs) - Electrolyte balance</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Hydrocortisone (₹80 Rs) - Steroid replacement; fludrocortisone (₹60 Rs) - Salt/fluid balance</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Never stop steroid replacement. Double the dose during illness or stress (sick-day rules). Wear a medical alert bracelet. Carry hydrocortisone injection training.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Endocrinologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Vitamin D Deficiency</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>bone pain, muscle weakness, fatigue, mood changes, frequent infections, hair loss, slow wound healing, joint stiffness</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Tila (sesame) (₹40 Rs) - Calcium and D support; Ashwagandha (₹120 Rs) - Strength; Sun exposure with morning sun</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Vitamin D3 supplements (₹60 Rs); calcium combined therapy; treat underlying cause</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Get 15-20 minutes of midday sunlight daily. Take supplements as prescribed. Eat fortified foods. Repeat blood test after 3 months.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>General Physician / Endocrinologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Vitamin B12 Deficiency</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>weakness, fatigue, numbness and tingling in hands and feet, pale skin, sore tongue, confusion, memory problems, balance issues, shortness of breath</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Nerve strength; Bala (₹70 Rs) - Tonic; green leafy vegetables in diet</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Vitamin B12 injections (₹80 Rs) or high-dose oral supplements; treat underlying cause</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Take B12 as prescribed (tablets or injections). Include fortified foods. For vegans, lifelong supplementation is needed. Repeat blood tests.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>General Physician / Hematologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease (CKD)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>fatigue, swelling in feet and ankles, puffiness around eyes, poor appetite, nausea, drowsiness, muscle cramps, Itching, reduced urine output, foamy urine</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Punarnava (₹70 Rs) - Supports kidneys; Gokshura (₹80 Rs) - Kidney tonic; Varuna (₹85 Rs) - Detoxifies</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ACE inhibitors / ARBs (₹60 Rs) - Protect kidneys; diuretics; erythropoietin for anemia; dialysis in advanced stage</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Control blood pressure and diabetes strictly. Low-sodium, low-protein diet. Avoid NSAIDs and self-medication. Regular nephrologist follow-up.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Nephrologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Glomerulonephritis</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>blood in urine (pink or cola-colored), foamy urine, swelling in face and legs, high blood pressure, reduced urine output, fatigue</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Punarnava (₹70 Rs) - Kidney health; Gokshura (₹80 Rs) - Urinary tonic; Varuna (₹85 Rs) - Anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Blood pressure medicines (ACE inhibitors); steroids or immunosuppressants; diuretics for swelling</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Strictly control blood pressure. Low-salt diet. Rest during acute phase. Treat strep infections promptly. Regular kidney function tests.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Nephrologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Pyelonephritis (Kidney Infection)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>high fever with chills, flank or back pain, painful urination, frequent urination, nausea, vomiting, cloudy or foul-smelling urine, blood in urine</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Gokshura (₹80 Rs) - Urinary tract support; Punarnava (₹70 Rs) - Anti-inflammatory; Coriander seed water (₹20 Rs) - Cooling</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Antibiotics (Ciprofloxacin ₹40 Rs); IV antibiotics for severe cases; pain relievers</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Complete the full antibiotic course. Drink plenty of water. Rest. Repeat urine test after treatment. Urgent care for high fever and vomiting.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Urologist / Nephrologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Nephrotic Syndrome</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>severe swelling in legs and around eyes, foamy urine, weight gain from fluid, fatigue, loss of appetite, high cholesterol</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Punarnava (₹70 Rs) - Reduces fluid; Gokshura (₹80 Rs) - Kidney health; Shatavari (₹90 Rs) - Protein restoration</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Steroids (Prednisolone ₹50 Rs); diuretics; ACE inhibitors; anticoagulants if needed</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Low-salt diet with controlled protein. Take steroids exactly as prescribed. Monitor weight daily. Regular urine protein tests.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Nephrologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Benign Prostatic Hyperplasia (BPH)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>frequent urination especially at night, difficulty starting urination, weak stream, dribbling, urgency, feeling of incomplete emptying, straining to urinate</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Gokshura (₹80 Rs) - Supports prostate; Ashwagandha (₹120 Rs) - Strengthens pelvic muscles; Saw palmetto-like herbal (Punarnava) (₹70 Rs)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Alpha-blockers (Tamsulosin ₹45 Rs) - Relax prostate; 5-alpha reductase inhibitors (Finasteride ₹60 Rs); surgery if severe</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Limit fluids before bed. Avoid caffeine and alcohol. Don't delay urination. Empty bladder fully. Urology follow-up and PSA monitoring.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Urologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Prostatitis</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>pain or burning on urination, frequent urgent urination, pain in pelvis or lower back, body aches, fever and chills, painful ejaculation, cloudy urine</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Gokshura (₹80 Rs) - Supports urinary health; Punarnava (₹70 Rs) - Anti-inflammatory; Jatamansi (₹90 Rs) - Pain relief</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Antibiotics (Ciprofloxacin ₹40 Rs, Doxycycline ₹70 Rs); alpha-blockers; anti-inflammatories</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Finish all antibiotics. Drink plenty of fluids. Warm sitz baths for comfort. Avoid alcohol and spicy food. Rest during acute phase.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Urologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>difficulty achieving or maintaining erection, reduced sexual desire, premature ejaculation, performance anxiety, underlying diabetes or heart disease</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Libido and stamina; Kapikachhu (₹90 Rs) - Improves sexual function; Shatavari (₹90 Rs) - Balance</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sildenafil (₹70 Rs) - On-demand therapy; Tadalafil (₹90 Rs); treat underlying cardiovascular cause; psychosexual therapy</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Address the underlying cause (diabetes, heart disease, stress). Exercise regularly. Limit alcohol and smoking. Openly consult your doctor.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Urologist / Sexologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Otitis Media (Middle Ear Infection)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ear pain especially at night, tugging at ear in children, fever, fluid draining from ear, difficulty hearing, irritability, poor sleep</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Warm garlic oil drops (₹40 Rs) - Antibacterial; Neem drops (₹35 Rs) - Antiseptic; Dashamoola (₹90 Rs) - Reduces inflammation</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Amoxicillin (₹50 Rs) - Antibiotic; Paracetamol (₹15 Rs) - Pain and fever; ear drops if eardrum is intact only on advice</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Finish the full antibiotic course. Apply warm compress to the ear. Keep ears dry. See ENT if pain persists or fluid drains.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ENT Specialist (Otorhinolaryngologist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Tinnitus</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ringing, buzzing, hissing or roaring sound in ears, ringing worse in silence, hearing loss, dizziness, difficulty concentrating, sleep disturbance</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Brahmi (₹90 Rs) - Inner ear nerve support; Ashwagandha (₹120 Rs) - Stress relief; white noise with relaxing music</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Treat underlying cause; hearing aids for hearing loss; sound therapy; stress management and low-dose medication</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Avoid loud noises and use ear protection. Reduce caffeine and alcohol. Manage stress with relaxation. Mask the sound with white noise.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ENT Specialist (Otorhinolaryngologist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Cataract</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>blurry or cloudy vision, sensitivity to light and glare, fading of colors, trouble with night vision, halos around lights, frequent prescription changes</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Triphala eye wash (₹50 Rs) - Eye tonic; Amalaki (₹50 Rs) - Antioxidant; Licorice drops (₹40 Rs) - Cooling</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Cataract surgery with lens implant; no medication dissolves cataract</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Use sunglasses to reduce glare. Get regular eye checks. Managing diabetes well. Surgery is safe and restores vision when ready.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ophthalmologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Glaucoma</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>often no early symptoms, gradual loss of peripheral vision, tunnel vision, eye pain, halos around lights, headache, red eye, blurred vision</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Triphala eye wash (₹50 Rs) - Eye health; Jyotishmati oil (₹70 Rs) - Optic nerve support; Manage stress and sleep</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Latanoprost eye drops (₹120 Rs) - Reduce eye pressure; timolol drops; laser or surgery if needed</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Use eye drops daily without skipping. Regular eye-pressure monitoring. Avoid heavy lifting and inverted postures. Family history needs screening.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Ophthalmologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Age-Related Macular Degeneration</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>blurred central vision, difficulty reading, colors looking dull, difficulty recognizing faces, straight lines appearing wavy, dark spots in vision</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Amalaki (₹50 Rs) - Antioxidant; Triphala (₹50 Rs) - Eye tonic; lutein-rich spinach and greens in diet</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Anti-VEGF injections for wet AMD (₹2500 Rs); vitamin supplements AREDS2; low-vision aids</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Eat leafy greens and omega-3s. Protect eyes from sun with sunglasses. Stop smoking. Regular retina examinations.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ophthalmologist (Retina Specialist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Stye (Hordeolum)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>painful red bump on eyelid, swelling, tenderness, tearing, crusting on eyelid, feeling of something in eye, light sensitivity</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Warm Triphala compress (₹50 Rs) - Soothes; Rose water eye rinse (₹30 Rs); Neem water wash (₹25 Rs)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Warm compresses; antibiotic eye drops (Moxifloxacin ₹80 Rs); rarely surgical drainage</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Apply warm compresses 4-5 times daily. Don't squeeze the stye. Wash hands and avoid eye makeup. See an eye doctor if it persists.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ophthalmologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Dry Eye Syndrome</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>burning or stinging eyes, feeling of grit in eyes, redness, blurred vision, tearing, discomfort in wind or screens, sensitivity to light</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Triphala eye wash (₹50 Rs) - Cooling; Rose water drops (₹30 Rs) - Soothes; Castor oil eye application at lid margin (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Artificial tears (₹80 Rs); cyclosporine eye drops for inflammation; punctal plugs if severe</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Blink often and take screen breaks (20-20-20 rule). Use a humidifier. Protect eyes in wind and sun. Warm lid compresses.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Ophthalmologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Corneal Ulcer (Keratitis)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>eye pain, redness, excessive watering, discharge, blurred vision, sensitivity to light, feeling of something in eye, white spot on cornea</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>This is urgent - Triphala wash only after doctor advice; Rose water protection after healing</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Antibacterial / antifungal eye drops every hour (Moxifloxacin ₹80 Rs, Natamycin ₹200 Rs); cycloplegics; urgent ophthalmology</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Seek urgent ophthalmologist care. Never wear contact lenses while sleeping. Maintain lens hygiene. Avoid rubbing eyes.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Ophthalmologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Contact Dermatitis</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>red rash at the contact site, itching, burning, dry cracked skin, blisters, swelling, oozing, tenderness</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Neem paste (₹35 Rs) - Soothes the skin; Aloe vera gel (₹40 Rs) - Cooling; Turmeric paste (₹40 Rs) - Anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Hydrocortisone cream (₹35 Rs) - Reduces inflammation; antihistamines (Cetirizine ₹20 Rs); avoid the allergen</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Identify and avoid the triggering substance. Apply cool compresses. Wash the area with mild soap. Use gloves with chemicals.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Seborrheic Dermatitis (Dandruff)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>flaky dandruff, oily scaly patches on scalp, itching, redness, flakes on eyebrows and sides of nose, cradle cap in infants</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Neem scalp oil (₹50 Rs) - Antifungal; Reetha (soapnut) wash (₹40 Rs) - Cleanses scalp; Aloe vera scalp mask (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Ketoconazole shampoo (₹80 Rs) - Antifungal; selenium sulfide shampoo; steroid lotion for flares</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Wash hair regularly with medicated shampoo. Avoid harsh styling products. Manage stress. Don't scratch and pick flakes.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Rosacea</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>persistent facial redness, visible blood vessels, red bumps and pimples, eye irritation and dryness, thickened skin, flushing with triggers</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Aloe vera gel (₹40 Rs) - Calms redness; Neem face pack (₹35 Rs) - Antibacterial; cooling cucumber mask (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Metronidazole gel (₹100 Rs) - Topical; doxycycline (₹90 Rs) - Oral; laser for redness</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Protect skin with sunscreen daily. Avoid spicy foods, alcohol and heat. Use gentle cleansers. Track your trigger factors.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Vitiligo</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>white patches of skin on face, hands, knees, symmetrical patches, premature greying of hair, depigmentation around mouth and eyes</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bakuchi oil (₹70 Rs) - Repigmentation; Manjistha (₹80 Rs) - Blood purifier; Neem capsules (₹60 Rs) - Immune balance</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Topical corticosteroids; phototherapy (NB-UVB ₹200 Rs); tacrolimus ointment; skin grafting in selective cases</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Prevent sunburn on patches with sunscreen. Consider phototherapy consistently. Camouflage with makeup if desired. Psychological support helps.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Alopecia Areata</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>sudden round patches of hair loss on scalp, hair loss in other body areas, patchy bald spots, itching or tingling before patches, changes in nails</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Bhringraj oil (₹70 Rs) - Hair growth; Amla and reetha wash (₹40 Rs) - Scalp health; Ashwagandha (₹120 Rs) - Stress reduction</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Minoxidil (₹50 Rs) - Hair growth; intralesional steroid injections; contact immunotherapy for extensive loss</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Manage stress which often triggers it. Use prescribed treatments regularly. Gentle hair care. Most patches regrow spontaneously.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Urticaria (Hives)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>raised itchy welts on skin, red or skin-colored bumps, swelling that comes and goes, burning or stinging, welts lasting hours</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Neem paste (₹35 Rs) - Soothes; Cooling aloe vera gel (₹40 Rs); Coriander and fennel cooling drink (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Antihistamines (Cetirizine ₹20 Rs, Fexofenadine ₹30 Rs); steroid short course for severe; identify triggers</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Identify and avoid triggers (foods, stress, heat). Take antihistamines as prescribed. Cool baths reduce itching. Seek care for swelling of lips or breathing difficulty.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Dermatologist / Allergist</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Boil (Furuncle)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>painful red swollen lump under skin, growing tender over days, white or yellow center, pus drainage, fever, redness around boil</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Neem and turmeric paste (₹35 Rs) - Draws out infection; warm Triphala compress (₹30 Rs); Guduchi (₹60 Rs) - Immune support</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Warm compresses; incision and drainage by a doctor; antibiotics (Cloxacillin ₹50 Rs) if infection spreads</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Apply warm compresses to encourage drainage. Never squeeze - let a doctor drain it. Keep the area clean. Recurrent boils need evaluation.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Dermatologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Athlete's Foot (Tinea Pedis)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>itchy scaly rash between toes, peeling cracked skin, burning and stinging, blisters, raw skin, foul smell, thickened toenails</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Neem oil (₹50 Rs) - Antifungal; tea tree oil application (₹70 Rs); keep feet dry with Triphala dusting powder (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Terbinafine cream (₹90 Rs) - Antifungal; Clotrimazole powder; oral terbinafine for stubborn cases</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Keep feet clean and dry, especially between toes. Wear breathable footwear. Change socks daily. Don't walk barefoot in public showers.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Impetigo</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>red sores that rupture and ooze, honey-colored crusts, blisters on face and limbs, itchy sores, sores spreading to other areas, swollen lymph nodes</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Neem and turmeric paste (₹35 Rs) - Antibacterial; Manjistha (₹80 Rs) - Blood purifier; gentle Triphala wash (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Topical mupirocin (₹90 Rs) - Antibacterial; oral antibiotics (Cephalexin ₹60 Rs) for extensive cases</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Wash sores gently and cover them. Complete antibiotics. Wash hands frequently. Don't share towels. Keep nails short to prevent spread.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Dermatologist / Pediatrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Warts</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>small rough raised bumps on skin, flesh-colored warts on hands and feet, black dots in wart, warts on soles painful while walking, cauliflower-like surface</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Neem paste (₹35 Rs) - Antiviral; garlic application (₹40 Rs) - Viral wart remedy; Kshara application by specialist</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Salicylic acid topical (₹60 Rs) - Peels the wart; cryotherapy (freezing); immunotherapy for stubborn warts</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Apply wart treatment consistently. Don't pick at warts. Wash hands after touching. Cover warts to prevent spread. See a doctor if persistent.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Dermatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Osteoarthritis</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>joint pain worsens with activity, morning stiffness under 30 minutes, grinding sensation in joint, swelling, reduced flexibility, bone spurs</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Shallaki (Boswellia) (₹110 Rs) - Anti-inflammatory; Guggulu (₹90 Rs) - Joint health; Mahanarayan oil massage (₹130 Rs)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Paracetamol (₹15 Rs) - Pain relief; topical NSAIDs; hyaluronic acid injections; joint replacement in severe cases</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Exercise with low-impact activities. Maintain a healthy weight. Use hot/cold therapy. Supportive footwear and canes reduce strain.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Rheumatologist / Orthopedic Surgeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Rheumatoid Arthritis</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>painful swollen joints on both sides, morning stiffness over an hour, fatigue, fever, weight loss, lumps under skin (rheumatoid nodules), dry eyes</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Shallaki (₹110 Rs) - Anti-inflammatory; Guggulu (₹90 Rs) - Joint relief; Ashwagandha (₹120 Rs) - Immune balance</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Methotrexate (₹80 Rs) - DMARD; hydroxychloroquine (₹50 Rs); biologics for severe disease; steroids short-term</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Start DMARDs early to prevent joint damage. Do gentle range-of-motion exercises. Balanced diet with omega-3s. Regular rheumatology follow-up.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Rheumatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Fibromyalgia</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>widespread muscle pain, fatigue, sleep problems, brain fog, tender points, headaches, irritable bowel symptoms, stiffness, sensitivity to pain</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Pain and fatigue; Brahmi (₹90 Rs) - Brain fog; warm Dashamoola oil massage (₹100 Rs)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Pregabalin (₹70 Rs) - Pain; duloxetine (₹90 Rs) - Pain and mood; graded exercise and CBT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pace your activities and avoid overexertion. Gentle exercise like yoga and walking. Good sleep hygiene. Cognitive behavioral therapy helps.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Rheumatologist / Pain Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Frozen Shoulder (Adhesive Capsulitis)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>stiffness and pain in one shoulder, limited range of motion, pain worse at night, difficulty with daily tasks, frozen then thawing phases</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Mahanarayan oil massage (₹130 Rs) - Shoulder mobility; Dashamoola (₹90 Rs) - Anti-inflammatory; warm compresses</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NSAIDs (Diclofenac ₹25 Rs) - Pain relief; physiotherapy; intra-articular steroid injections</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Do daily stretching exercises as guided. Heat before exercise, ice after. Keep moving the shoulder gently. Physiotherapy is key.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Orthopedic Surgeon / Physiotherapist</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Tennis Elbow (Lateral Epicondylitis)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>pain on the outer elbow, pain worsens with gripping or lifting, tenderness over the elbow bone, weak grip, pain radiating to forearm</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Nirgundi oil massage (₹100 Rs) - Local relief; Shallaki (₹110 Rs) - Anti-inflammatory; Turmeric paste compress (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NSAID gels (Diclofenac ₹80 Rs); physiotherapy; steroid injections; rarely surgery</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Rest the affected arm. Use a counterforce strap. Apply ice and do stretching. Modify your grip and lifting technique.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Orthopedic Surgeon / Physiotherapist</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Plantar Fasciitis</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>sharp heel pain with first steps in the morning, pain after long standing, heel tenderness, pain with stretching the foot, burning in sole</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Warm oil foot massage with Nirgundi (₹100 Rs) - Soothing; Turmeric foot soak (₹40 Rs); Dashamoola (₹90 Rs) - Anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Supportive footwear and orthotics; NSAIDs (Ibuprofen ₹25 Rs); plantar fascia stretching; shockwave therapy</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Stretch the calf and plantar fascia every morning. Wear cushioned shoes. Ice the heel after activity. Avoid walking barefoot on hard floors.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Orthopedic Surgeon / Physiotherapist</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Ankylosing Spondylitis</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>lower back pain and stiffness worse in the morning and with rest, improves with exercise, pain in buttocks, reduced flexibility, fatigue, eye inflammation</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Shallaki (₹110 Rs) - Anti-inflammatory; Guggulu (₹90 Rs) - Joint health; Dahmamoola (₹90 Rs) - Back support</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NSAIDs (Naproxen ₹30 Rs); biologics (Sulfasalazine ₹70 Rs, TNF inhibitors); physiotherapy</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Exercise daily - posture and stretching is vital. Sleep on a firm bed. Avoid prolonged sitting. Quit smoking. Regular rheumatology care.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Rheumatologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Tooth Decay (Dental Caries)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>toothache, sensitivity to hot cold and sweet, visible holes in teeth, pain on biting, white or brown spots on teeth, bad taste</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Clove oil application (₹40 Rs) - Pain relief; Triphala mouth rinse (₹50 Rs) - Antiseptic; Licorice mouth rinse (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Fluoride treatment; dental fillings; root canal for deep decay; extraction for unsalvageable teeth</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Brush twice daily with fluoride toothpaste. Limit sugary snacks. Floss daily. Visit the dentist every 6 months.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Dentist</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Gingivitis</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>bleeding gums while brushing, red swollen gums, bad breath, tender gums, receding gums, gum tenderness</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Triphala powder rinse (₹50 Rs) - Antiseptic; Aloe vera gum massage (₹40 Rs); Neem stick brushing (₹30 Rs)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Professional cleaning (scaling); improved oral hygiene; medicated mouthwash (Chlorhexidine ₹60 Rs)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Brush and floss properly twice daily. Use an antiseptic mouthwash. Get professional scaling. Stop smoking which worsens gum disease.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Dentist</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Periodontitis</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>bad breath, receding gums, loose teeth, painful chewing, red bleeding swollen gums, pus between teeth, change in bite</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Triphala mouth rinse (₹50 Rs) - Reduces gum inflammation; Neem and honey gum paste (₹35 Rs); Aloe vera massage (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Deep cleaning (scaling and root planing); antibiotics (Amoxicillin ₹50 Rs); surgery for advanced cases</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Commit to excellent oral hygiene. Professional deep cleaning. Quit smoking. Regular dental check-ups every 3-6 months.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Dentist (Periodontist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Tooth Abscess</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>severe throbbing toothache, pain radiating to jaw and ear, fever, swollen face or cheek, sensitivity to hot and cold, swollen gum, bad taste</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Clove oil (₹40 Rs) - Pain relief; warm Triphala salt water rinse (₹30 Rs); Guduchi (₹60 Rs) - Infection support</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Antibiotics (Amoxicillin ₹50 Rs); root canal or extraction; incision and drainage of the abscess</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>See a dentist immediately. Take prescribed antibiotics. Rinse with warm salt water. Pain relief for comfort.</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Dentist / Emergency Dental</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Canker Sore (Aphthous Ulcer)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>painful round shallow ulcers inside mouth, pain worse when eating or talking, burning sensation, white or yellow center with red border, recurrent sores</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Triphala mouth rinse (₹50 Rs) - Heals ulcers; Honey application (₹40 Rs) - Soothing; Yashtimadhu (₹80 Rs) - Reduces sores</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Topical anesthetic gels (Lignocaine ₹50 Rs); steroid mouthwashes; avoid triggers</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Avoid spicy, acidic and hard foods during outbreaks. Use a soft toothbrush. Manage stress. Rinse with warm salt water.</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Dentist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TMJ Disorder (Temporomandibular Joint)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>jaw pain or tenderness, pain in temple and ear, clicking or popping sounds on jaw movement, difficulty opening the mouth fully, facial pain, locking of jaw</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mahanarayan oil jaw massage (₹130 Rs) - Relaxes muscles; Dashamoola (₹90 Rs) - Anti-inflammatory; warm compress (₹20 Rs)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NSAIDs (Ibuprofen ₹25 Rs); muscle relaxants; mouth guards for grinding; physiotherapy</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Eat soft foods and avoid wide mouth opening. Use warm compresses and gentle jaw exercises. Manage teeth grinding with a mouthguard.</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Dentist / Maxillofacial Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Dysmenorrhea (Menstrual Cramps)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>cramping pain in lower abdomen during periods, pain radiating to back and thighs, nausea, diarrhea, headache, dizziness, fatigue</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ashwagandha (₹120 Rs) - Antispasmodic; warm Dashamoola oil massage on lower belly (₹100 Rs); ginger turmeric tea (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Ibuprofen (₹25 Rs) - Pain relief; naproxen for cramps; hormonal birth control if needed</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Apply a heating pad to the lower abdomen. Gentle exercise and stretching. Warm baths. Rest and hydration. See a gynaecologist for severe pain.</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Gynaecologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Menopause Syndrome</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>hot flashes, night sweats, irregular periods, mood swings, vaginal dryness, sleep problems, fatigue, weight gain, reduced libido</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Shatavari (₹90 Rs) - Hormonal balance; Ashwagandha (₹120 Rs) - Manages stress; black cohosh-like cooling herbs</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Hormone replacement therapy (HRT) when appropriate; vaginal moisturizers; antidepressants for hot flashes in some</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Exercise and a balanced diet rich in calcium and vitamin D. Manage stress with relaxation. Limit caffeine and spicy foods. Discuss HRT benefits with a doctor.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Gynaecologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>severe pelvic pain, painful periods, pain during intercourse, heavy bleeding, pain with urination or bowel movements, difficulty conceiving, fatigue</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Shatavari (₹90 Rs) - Hormone balance; Dashamoola (₹90 Rs) - Anti-inflammatory; Ashwagandha (₹120 Rs) - Pain support</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NSAIDs (₹25 Rs) - Pain; hormonal therapy (combined pills, GnRH agonists); laparoscopy surgery</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Manage pain with prescribed treatment. Gentle exercise and pelvic physiotherapy. Follow dietary anti-inflammatory choices. Fertility planning with specialist.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Gynaecologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Vaginal Candidiasis (Yeast Infection)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>itching and soreness around the vagina, thick white cottage-cheese discharge, burning during urination, pain during intercourse, redness and swelling</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Neem wash (₹35 Rs) - Antifungal; curd (probiotic) application under guidance; Haridra (Turmeric) (₹40 Rs) - Internal use</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Clotrimazole vaginal cream (₹100 Rs) - Antifungal; fluconazole oral tablet (₹70 Rs)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Keep the area clean and dry. Wear cotton underwear. Avoid scented products. Complete the antifungal treatment. See a gynaecologist for recurrent infection.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Gynaecologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Premenstrual Syndrome (PMS)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>mood swings, irritability, bloating, breast tenderness, fatigue, food cravings, headache, sleep problems, breast swelling, concentration difficulty</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Shatavari (₹90 Rs) - Hormone balance; Ashwagandha (₹120 Rs) - Mood support; ginger tea for bloating (₹40 Rs)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SSRIs for severe mood symptoms; NSAIDs for cramps; calcium and vitamin B6 supplements</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Exercise regularly and reduce salt and caffeine around periods. Eat smaller frequent meals. Manage stress. Track symptoms to predict them.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Gynaecologist / General Physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Heat Stroke</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>high body temperature (above 104F), hot dry skin, confusion, rapid heartbeat, rapid shallow breathing, nausea, vomiting, seizures, fainting</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>This is an emergency - Cool the body fast (cold water, ice packs), later Amalaki (₹50 Rs) - Rehydration support</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Emergency: rapid cooling in hospital, IV fluids, monitoring of organ function</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Call emergency services immediately. Move to shade and cool rapidly with cold water. Give sips of water if conscious. Never wait it out.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Emergency Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Dehydration</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>extreme thirst, dry mouth and lips, dark yellow urine, infrequent urination, dizziness, fatigue, sunken eyes, headache, rapid heartbeat, confusion</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Coconut water (₹20 Rs) - Natural electrolyte; Coriander seed water (₹20 Rs); warm Triphala water</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Oral rehydration salts (ORS ₹20 Rs); IV fluids for severe cases; treat underlying cause</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Drink fluids and ORS gradually. Avoid caffeine and alcohol. Monitor urine color. Seek care for confusion, weakness or inability to keep fluids down.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>General Physician / Emergency Medicine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
